--- a/app/data/dashboard teste.xlsx
+++ b/app/data/dashboard teste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admgs\OneDrive\Documentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admgs\Documentos\GitHub\projeto_contas_a_pagar_receber\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C01AD3-0EFA-4BCE-8332-6CF845078DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F66BBFB-F7C4-43B2-8235-F9573DB88719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4EF8221-4CEA-4B6C-B0E4-532E1587AB52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4EF8221-4CEA-4B6C-B0E4-532E1587AB52}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,15 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>FLUXO DE CAIXA PREVISTO</t>
   </si>
   <si>
     <t>18/08 a 21/08</t>
-  </si>
-  <si>
-    <t>SALDO INICIAL DO DIA</t>
   </si>
   <si>
     <t>18/08/2026</t>
@@ -148,7 +145,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="_-&quot;R$ &quot;* #,##0.00_-;&quot;-R$ &quot;* #,##0.00_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;R$ &quot;* #,##0.00_-;&quot;-R$ &quot;* #,##0.00_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -247,7 +244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -286,8 +283,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
@@ -297,62 +294,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,150 +525,138 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -760,7 +689,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>106974</xdr:rowOff>
+      <xdr:rowOff>116499</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -808,7 +737,7 @@
       <xdr:col>17</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>106974</xdr:rowOff>
+      <xdr:rowOff>116499</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1165,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5406B65-DEE8-467A-B69F-DB52EA16D365}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
@@ -1173,459 +1102,422 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="39"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="E6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="15">
-        <v>881772.77</v>
-      </c>
-      <c r="C5" s="16">
-        <f>B40</f>
-        <v>893594.91</v>
-      </c>
-      <c r="D5" s="16">
-        <f>C40</f>
-        <v>913722.08000000007</v>
-      </c>
-      <c r="E5" s="17">
-        <f>D40</f>
-        <v>919899.7300000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>23781.91</v>
+      </c>
+      <c r="C7" s="2">
+        <v>19850</v>
+      </c>
+      <c r="D7" s="2">
+        <v>12057.79</v>
+      </c>
+      <c r="E7" s="15">
+        <v>22951.38</v>
+      </c>
+    </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20"/>
+      <c r="A8" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>2815.24</v>
+      </c>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>6</v>
-      </c>
+      <c r="A9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4">
+        <v>361.04</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
+        <v>12353.1</v>
+      </c>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4">
-        <v>23781.91</v>
-      </c>
-      <c r="C10" s="4">
-        <v>19850</v>
-      </c>
-      <c r="D10" s="4">
-        <v>12057.79</v>
-      </c>
-      <c r="E10" s="24">
-        <v>22951.38</v>
-      </c>
+      <c r="A10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="21"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5">
-        <v>2815.24</v>
-      </c>
-      <c r="E11" s="26"/>
+      <c r="A11" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="6">
+        <v>220.92</v>
+      </c>
+      <c r="C11" s="6">
+        <v>500</v>
+      </c>
+      <c r="D11" s="6">
+        <v>272.99</v>
+      </c>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6">
-        <v>361.04</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6">
-        <v>12353.1</v>
-      </c>
-      <c r="E12" s="28"/>
+      <c r="A12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>308</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="15"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="30"/>
+      <c r="A13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="15"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8">
-        <v>220.92</v>
-      </c>
-      <c r="C14" s="8">
-        <v>500</v>
-      </c>
-      <c r="D14" s="8">
-        <v>272.99</v>
-      </c>
-      <c r="E14" s="32"/>
+      <c r="A14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1642</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4">
-        <v>308</v>
-      </c>
+      <c r="A15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="24"/>
+      <c r="D15" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>2800.2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>600.46</v>
+      </c>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1642</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="26"/>
+      <c r="A17" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6">
+        <v>2836.77</v>
+      </c>
+      <c r="D17" s="6">
+        <v>8923.2999999999993</v>
+      </c>
+      <c r="E17" s="23"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="E18" s="28">
-        <v>0.01</v>
+      <c r="A18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="15">
+        <v>557600</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7">
-        <v>2800.2</v>
-      </c>
-      <c r="D19" s="7">
-        <v>600.46</v>
-      </c>
-      <c r="E19" s="30"/>
+      <c r="A19" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2">
+        <v>41845</v>
+      </c>
+      <c r="E19" s="15"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8">
-        <v>2836.77</v>
-      </c>
-      <c r="D20" s="8">
-        <v>8923.2999999999993</v>
-      </c>
-      <c r="E20" s="32"/>
+      <c r="A20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
-        <v>20</v>
+      <c r="A21" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="24">
-        <v>557600</v>
-      </c>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4">
-        <v>41845</v>
-      </c>
-      <c r="E22" s="24"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="26"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A22" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="28"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="21"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="30"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="31" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6">
+        <v>664.43</v>
+      </c>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8">
-        <v>664.43</v>
-      </c>
-      <c r="E26" s="32"/>
-    </row>
+      <c r="B24" s="25">
+        <f>SUM(B7:B23)</f>
+        <v>26313.87</v>
+      </c>
+      <c r="C24" s="25">
+        <f>SUM(C7:C23)</f>
+        <v>25986.97</v>
+      </c>
+      <c r="D24" s="25">
+        <f>SUM(D7:D23)</f>
+        <v>79532.329999999987</v>
+      </c>
+      <c r="E24" s="26">
+        <f>SUM(E7:E23)</f>
+        <v>580551.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="34">
-        <f>SUM(B10:B26)</f>
-        <v>26313.87</v>
-      </c>
-      <c r="C27" s="34">
-        <f>SUM(C10:C26)</f>
-        <v>25986.97</v>
-      </c>
-      <c r="D27" s="34">
-        <f>SUM(D10:D26)</f>
-        <v>79532.329999999987</v>
-      </c>
-      <c r="E27" s="35">
-        <f>SUM(E10:E26)</f>
-        <v>580551.39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="46" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="42"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="48"/>
+      <c r="B28" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7">
+        <v>15095.97</v>
+      </c>
+      <c r="C29" s="7">
+        <v>24815.919999999998</v>
+      </c>
+      <c r="D29" s="7">
+        <v>50209.98</v>
+      </c>
+      <c r="E29" s="28">
+        <v>43857.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7">
+        <v>2226.7199999999998</v>
+      </c>
+      <c r="C30" s="7">
+        <v>851.74</v>
+      </c>
+      <c r="D30" s="7">
+        <v>15500</v>
+      </c>
+      <c r="E30" s="28">
+        <v>8082.72</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="44" t="s">
+      <c r="A31" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7">
+        <v>813.32</v>
+      </c>
+      <c r="C31" s="7">
+        <v>446.48</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="28"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7">
+        <v>20000</v>
+      </c>
+      <c r="C32" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D32" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E32" s="28">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="30">
+        <f>SUM(B29:B32)</f>
+        <v>38136.009999999995</v>
+      </c>
+      <c r="C33" s="30">
+        <f>SUM(C29:C32)</f>
+        <v>46114.14</v>
+      </c>
+      <c r="D33" s="30">
+        <f>SUM(D29:D32)</f>
+        <v>85709.98000000001</v>
+      </c>
+      <c r="E33" s="31">
+        <f>SUM(E29:E32)</f>
+        <v>71940.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="D36" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="E36" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E31" s="45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="9">
-        <v>15095.97</v>
-      </c>
-      <c r="C32" s="9">
-        <v>24815.919999999998</v>
-      </c>
-      <c r="D32" s="9">
-        <v>50209.98</v>
-      </c>
-      <c r="E32" s="39">
-        <v>43857.62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="9">
-        <v>2226.7199999999998</v>
-      </c>
-      <c r="C33" s="9">
-        <v>851.74</v>
-      </c>
-      <c r="D33" s="9">
-        <v>15500</v>
-      </c>
-      <c r="E33" s="39">
-        <v>8082.72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" s="9">
-        <v>813.32</v>
-      </c>
-      <c r="C34" s="9">
-        <v>446.48</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="39"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="9">
-        <v>20000</v>
-      </c>
-      <c r="C35" s="9">
-        <v>20000</v>
-      </c>
-      <c r="D35" s="9">
-        <v>20000</v>
-      </c>
-      <c r="E35" s="39">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="41">
-        <f>SUM(B32:B35)</f>
-        <v>38136.009999999995</v>
-      </c>
-      <c r="C36" s="41">
-        <f>SUM(C32:C35)</f>
-        <v>46114.14</v>
-      </c>
-      <c r="D36" s="41">
-        <f>SUM(D32:D35)</f>
-        <v>85709.98000000001</v>
-      </c>
-      <c r="E36" s="42">
-        <f>SUM(E32:E35)</f>
-        <v>71940.34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
-      <c r="B40" s="16">
-        <f>B5+B36-B27</f>
-        <v>893594.91</v>
-      </c>
-      <c r="C40" s="16">
-        <f>C5+C36-C27</f>
-        <v>913722.08000000007</v>
-      </c>
-      <c r="D40" s="16">
-        <f>D5+D36-D27</f>
-        <v>919899.7300000001</v>
-      </c>
-      <c r="E40" s="17">
-        <f>E5+E36-E27</f>
-        <v>411288.68000000005</v>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="44"/>
+      <c r="B37" s="10" t="e">
+        <f>#REF!+B33-B24</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C37" s="10" t="e">
+        <f>#REF!+C33-C24</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D37" s="10" t="e">
+        <f>#REF!+D33-D24</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E37" s="11" t="e">
+        <f>#REF!+E33-E24</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
+    <mergeCell ref="A36:A37"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
